--- a/data/trans_orig/IP08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP08-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21778</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>34273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90682</t>
+          <t>90187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100179</t>
+          <t>100058</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99602</t>
+          <t>98926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111233</t>
+          <t>110668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193292</t>
+          <t>193278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208868</t>
+          <t>208698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>32826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43859</t>
+          <t>44309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>48698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72375</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>220455</t>
+          <t>220379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>235397</t>
+          <t>235233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209897</t>
+          <t>209447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227677</t>
+          <t>227194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434586</t>
+          <t>435052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>457504</t>
+          <t>458263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20569</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,49 +1434,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9683</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22717</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>16,13%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9679</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21741</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>42</t>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21079</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37473</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106979</t>
+          <t>106177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118485</t>
+          <t>118458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,47 +1547,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>83,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>125782</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>118103</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>131137</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>83,87%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>125782</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>119079</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>131141</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,32%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>84,56%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230895</t>
+          <t>230246</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247289</t>
+          <t>246688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33965</t>
+          <t>34620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181274</t>
+          <t>180622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190064</t>
+          <t>189871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180514</t>
+          <t>180596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194010</t>
+          <t>194152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366181</t>
+          <t>365526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381430</t>
+          <t>381726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>45465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69713</t>
+          <t>69555</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>98523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123077</t>
+          <t>120983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160145</t>
+          <t>159801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>611876</t>
+          <t>612448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>636661</t>
+          <t>635556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>624037</t>
+          <t>623482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>652292</t>
+          <t>652450</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1242881</t>
+          <t>1243225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1279949</t>
+          <t>1282043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27973</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32766</t>
+          <t>33630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36350</t>
+          <t>37249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56823</t>
+          <t>56912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118054</t>
+          <t>116789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130977</t>
+          <t>131044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113224</t>
+          <t>112360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127456</t>
+          <t>127483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>235105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255667</t>
+          <t>254768</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37203</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48278</t>
+          <t>50071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54048</t>
+          <t>55199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80166</t>
+          <t>80129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199047</t>
+          <t>200053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>215035</t>
+          <t>216059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220713</t>
+          <t>218920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240183</t>
+          <t>238377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425075</t>
+          <t>425112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451193</t>
+          <t>450042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>26147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44724</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129615</t>
+          <t>129620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142648</t>
+          <t>143404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>136142</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148869</t>
+          <t>148988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270890</t>
+          <t>271113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>288924</t>
+          <t>289467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28513</t>
+          <t>28823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48151</t>
+          <t>47173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151601</t>
+          <t>151020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162734</t>
+          <t>162855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148429</t>
+          <t>147339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163452</t>
+          <t>162658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303141</t>
+          <t>304119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322779</t>
+          <t>322469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97881</t>
+          <t>97242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87689</t>
+          <t>87486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118812</t>
+          <t>116351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164766</t>
+          <t>164447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207436</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612776</t>
+          <t>613415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>639941</t>
+          <t>641064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634695</t>
+          <t>637156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>665818</t>
+          <t>666021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1256728</t>
+          <t>1258420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1299398</t>
+          <t>1299717</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>14962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115976</t>
+          <t>116215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125783</t>
+          <t>125324</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105494</t>
+          <t>105381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>115998</t>
+          <t>116011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224875</t>
+          <t>224969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239229</t>
+          <t>239665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25689</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28960</t>
+          <t>29069</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30497</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>50274</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183927</t>
+          <t>184520</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196514</t>
+          <t>197042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226028</t>
+          <t>225919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240889</t>
+          <t>240215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414544</t>
+          <t>414330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434107</t>
+          <t>433842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173737</t>
+          <t>173472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183844</t>
+          <t>183964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177936</t>
+          <t>178009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186232</t>
+          <t>186279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355417</t>
+          <t>355471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>368164</t>
+          <t>368135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>32061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155856</t>
+          <t>154440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166604</t>
+          <t>166586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155568</t>
+          <t>156413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166845</t>
+          <t>167424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315304</t>
+          <t>314522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330747</t>
+          <t>330903</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58633</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41248</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>62554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>115865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>643595</t>
+          <t>642674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>665079</t>
+          <t>664994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>678064</t>
+          <t>679218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>700524</t>
+          <t>701318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1329847</t>
+          <t>1328135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1361228</t>
+          <t>1360756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26340</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>45088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43423</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54041</t>
+          <t>54637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92615</t>
+          <t>92642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104788</t>
+          <t>104593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144465</t>
+          <t>144029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153758</t>
+          <t>153477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>152069</t>
+          <t>151910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>166328</t>
+          <t>167349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300470</t>
+          <t>300928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>318378</t>
+          <t>317852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>34091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30519</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51705</t>
+          <t>51539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148733</t>
+          <t>148200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162339</t>
+          <t>162302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180038</t>
+          <t>178399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196796</t>
+          <t>196993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333858</t>
+          <t>334024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355044</t>
+          <t>355901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48130</t>
+          <t>48746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>27264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72497</t>
+          <t>78653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52292</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107939</t>
+          <t>106618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226884</t>
+          <t>226268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>255884</t>
+          <t>256465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230998</t>
+          <t>224842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276480</t>
+          <t>276231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>470570</t>
+          <t>471891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>526217</t>
+          <t>526622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>49148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83860</t>
+          <t>82883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131983</t>
+          <t>133640</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138048</t>
+          <t>137584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>208543</t>
+          <t>200782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581036</t>
+          <t>582013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>615215</t>
+          <t>615748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>628001</t>
+          <t>626344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>679338</t>
+          <t>679480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1216338</t>
+          <t>1224099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1286833</t>
+          <t>1287297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP08-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15530</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10526</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22107</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,79%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10005</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6113</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15984</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5653</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15290</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,42%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15530</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10712</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22454</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>18555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34273</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>105850</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>99273</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>110854</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,21%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>96166</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>90187</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>100058</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>90881</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>100518</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,58%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>105850</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>98926</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>110668</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,21%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193278</t>
+          <t>192415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208698</t>
+          <t>208996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26592</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44085</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24665</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17972</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32826</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18009</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33173</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,74%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>26562</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>44309</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48698</t>
+          <t>48212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71909</t>
+          <t>71762</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>218615</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>209671</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>227164</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>228540</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>220379</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>235233</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>220032</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>235196</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,26%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>218615</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>209447</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>227194</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>435052</t>
+          <t>435199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>458263</t>
+          <t>458749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9602</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22043</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13699</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21371</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8593</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20494</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9683</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22717</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>37964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>125782</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>118777</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131218</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>113849</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>106177</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>118458</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>107054</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,26%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>125782</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>118103</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>131137</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230246</t>
+          <t>230404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>246688</t>
+          <t>247699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>140820</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140820</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>140820</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>140820</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>140820</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>140820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12087</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25179</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7874</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4226</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13475</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13868</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11897</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25453</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34620</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>188280</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>180870</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>193962</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>186223</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>180622</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>189871</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>180229</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>189637</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>188280</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>180596</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>194152</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365526</t>
+          <t>365721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381726</t>
+          <t>381725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>70691</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>97757</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45465</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68573</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>45625</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>69264</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>69555</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>98523</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120983</t>
+          <t>122977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159801</t>
+          <t>158856</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>638527</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>624248</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>651314</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>935</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>624778</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>612448</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>635556</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>611757</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>635396</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>638527</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>623482</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>652450</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1243225</t>
+          <t>1244170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1282043</t>
+          <t>1280049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722005</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722005</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722005</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722005</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722005</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722005</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24939</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17996</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32637</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21008</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14983</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29238</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14791</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28564</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24939</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18507</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37249</t>
+          <t>37243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56912</t>
+          <t>56444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121051</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>113353</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>127994</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>125019</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>116789</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131044</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>117463</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>131236</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>85,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121051</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>112360</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>127483</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,92%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235105</t>
+          <t>235573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254768</t>
+          <t>254774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146027</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146027</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146027</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29641</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48268</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,02%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>28288</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20191</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36197</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20966</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36989</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,97%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>38421</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>30614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>50071</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55199</t>
+          <t>55037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80129</t>
+          <t>79674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>230570</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>220723</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>239350</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207962</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200053</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>216059</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>199261</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>215284</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,03%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>230570</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>218920</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>238377</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425112</t>
+          <t>425567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450042</t>
+          <t>450204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9907</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22185</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>20199</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13639</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27423</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13677</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>28206</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9583</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22429</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26147</t>
+          <t>26740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44501</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>143610</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>136386</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148664</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136844</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>129620</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>143404</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>128837</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>143366</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>143610</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>136142</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148988</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>271113</t>
+          <t>271358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>289467</t>
+          <t>288874</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24098</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17365</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32422</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13375</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8482</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20317</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8488</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>4,95%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24098</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>17297</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32616</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>27996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47173</t>
+          <t>48032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155857</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>147533</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>162590</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>157962</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>151020</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>162855</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>151479</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>162849</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>95,05%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>155857</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>147339</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>162658</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,61%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>81,88%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>90,39%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>453</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304119</t>
+          <t>303260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322469</t>
+          <t>323296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>85622</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>117859</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>69593</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>97242</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>70360</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>96227</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>87486</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>116351</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164447</t>
+          <t>165806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205744</t>
+          <t>207696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>651088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>635648</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>667885</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>627788</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>613415</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>641064</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>614430</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>640297</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>651088</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>637156</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>666021</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1258420</t>
+          <t>1256468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1299717</t>
+          <t>1298358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710657</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710657</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710657</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18882</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9682</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5853</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14962</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5624</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15880</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8153</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18783</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>111533</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>105282</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>116176</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>121495</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>116215</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>125324</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>115297</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>125553</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,62%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>111533</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>105381</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>116011</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224969</t>
+          <t>224999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239665</t>
+          <t>239392</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131177</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131177</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131177</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14395</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28589</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18516</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12574</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25096</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12937</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>25993</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,83%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14773</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29069</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>30730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50274</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>233919</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>226399</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>240593</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>191100</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>184520</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>197042</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>183623</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>196679</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,17%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>233919</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>225919</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>240215</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414330</t>
+          <t>414700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>433842</t>
+          <t>433874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>254988</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>254988</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>254988</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>209616</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>209616</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>209616</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>254988</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>254988</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>254988</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10915</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8903</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4935</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15427</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14728</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2293</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10563</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>23493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>182641</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>177657</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>185821</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>179996</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>173472</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>183964</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>174171</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>184005</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>182641</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>178009</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>186279</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355471</t>
+          <t>353978</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>368135</t>
+          <t>367897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6834</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18863</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5949</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18095</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16759</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6624</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17635</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>162232</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>155185</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>167214</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>161990</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>154440</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166586</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>155776</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>166427</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,89%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>162232</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>156413</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>167424</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314522</t>
+          <t>315553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330903</t>
+          <t>331269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41347</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63119</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>47647</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>37234</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>59554</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>36956</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>59632</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>40454</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>62554</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83244</t>
+          <t>84660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115865</t>
+          <t>116464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690325</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>678653</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>700425</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>654581</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>642674</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>664994</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>642596</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>665272</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>690325</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>679218</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>701318</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1328135</t>
+          <t>1327536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1360756</t>
+          <t>1359340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>702228</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>702228</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>702228</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6036</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13681</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4673</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12423</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41136</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36856</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>44501</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>49338</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45088</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52838</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85,79%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>44302</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44767</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54637</t>
+          <t>47755</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>99333</t>
+          <t>85438</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92642</t>
+          <t>79421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>90820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13343</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26187</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5822</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15270</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>36459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>138619</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>131335</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>144179</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>150007</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>144029</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>153477</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>159895</t>
+          <t>136629</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151910</t>
+          <t>131413</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167349</t>
+          <t>139992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>309903</t>
+          <t>275247</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300928</t>
+          <t>266580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>317852</t>
+          <t>281857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14362</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31340</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10770</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24872</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51539</t>
+          <t>49588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>178575</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>168786</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>185764</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>156334</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>148200</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>162302</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>189061</t>
+          <t>157604</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178399</t>
+          <t>149035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196993</t>
+          <t>163441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>345396</t>
+          <t>336179</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334024</t>
+          <t>325210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355901</t>
+          <t>346153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26896</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65940</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18549</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>48746</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78653</t>
+          <t>34254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106618</t>
+          <t>94571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>251425</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>224501</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>263545</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>245668</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>226268</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>256465</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>262003</t>
+          <t>230832</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224842</t>
+          <t>221915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276231</t>
+          <t>238669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>507671</t>
+          <t>482256</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>471891</t>
+          <t>452038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>526622</t>
+          <t>496393</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>290441</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>290441</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>290441</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>275014</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>275014</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>275014</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>256169</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>256169</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>256169</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>578509</t>
+          <t>546609</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>578509</t>
+          <t>546609</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>578509</t>
+          <t>546609</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>71419</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>114800</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49148</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>82883</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80504</t>
+          <t>47941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133640</t>
+          <t>71961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137584</t>
+          <t>125646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200782</t>
+          <t>178982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>609754</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>583825</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>627206</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>852</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>601348</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>582013</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>615748</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>660955</t>
+          <t>569366</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>626344</t>
+          <t>556487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>679480</t>
+          <t>580507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1262303</t>
+          <t>1179120</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1224099</t>
+          <t>1148091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1287297</t>
+          <t>1201427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>698625</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664896</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664896</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664896</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>628448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>628448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>759984</t>
+          <t>628448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1327073</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1327073</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1327073</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
